--- a/templates/CAPIT AQUILA 6 - template.xlsx
+++ b/templates/CAPIT AQUILA 6 - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$6:$H$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$6:$H$44</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -815,11 +815,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1238,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="51" min="1" max="1"/>
@@ -1246,8 +1246,8 @@
     <col width="5.42578125" customWidth="1" style="51" min="9" max="9"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="51" min="10" max="10"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="51" min="11" max="11"/>
-    <col width="9.140625" customWidth="1" style="51" min="12" max="25"/>
-    <col width="9.140625" customWidth="1" style="51" min="26" max="16384"/>
+    <col width="9.140625" customWidth="1" style="51" min="12" max="26"/>
+    <col width="9.140625" customWidth="1" style="51" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1393,14 +1393,14 @@
       <c r="A19" s="3" t="n"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C19" s="30" t="n">
-        <v>3.55189716</v>
+        <v>3.57580901</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.0002127006005840926</v>
+        <v>0.0003476953419927487</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>0.0005426623598601132</v>
@@ -1409,10 +1409,10 @@
         <v>0.0006017779632476739</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>0.3919575344030167</v>
+        <v>0.64072131717847</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.3534536217248476</v>
+        <v>0.5777801169659109</v>
       </c>
       <c r="I19" s="3" t="n"/>
     </row>
@@ -1420,14 +1420,14 @@
       <c r="A20" s="3" t="n"/>
       <c r="B20" s="38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C20" s="39" t="n">
-        <v>3.55114183</v>
+        <v>3.57456615</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>-0.001226493256735295</v>
+        <v>0.003642783860219989</v>
       </c>
       <c r="E20" s="40" t="n">
         <v>0.0005426623598601132</v>
@@ -1436,10 +1436,10 @@
         <v>0.0006017779632476739</v>
       </c>
       <c r="G20" s="41" t="n">
-        <v>-2.260140646297006</v>
+        <v>6.712799946469516</v>
       </c>
       <c r="H20" s="41" t="n">
-        <v>-2.038115935844774</v>
+        <v>6.053368655376847</v>
       </c>
       <c r="I20" s="3" t="n"/>
     </row>
@@ -1447,14 +1447,14 @@
       <c r="A21" s="3" t="n"/>
       <c r="B21" s="38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C21" s="39" t="n">
-        <v>3.55550263</v>
+        <v>3.56159204</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>0.0002213847950318648</v>
+        <v>0.0001939958323582402</v>
       </c>
       <c r="E21" s="40" t="n">
         <v>0.0005426623598601132</v>
@@ -1463,10 +1463,10 @@
         <v>0.0006017779632476739</v>
       </c>
       <c r="G21" s="41" t="n">
-        <v>0.4079604767298272</v>
+        <v>0.3574890147314588</v>
       </c>
       <c r="H21" s="41" t="n">
-        <v>0.3678845164703205</v>
+        <v>0.3223711139425645</v>
       </c>
       <c r="I21" s="3" t="n"/>
     </row>
@@ -1474,14 +1474,14 @@
       <c r="A22" s="3" t="n"/>
       <c r="B22" s="38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C22" s="39" t="n">
-        <v>3.55471567</v>
+        <v>3.56090124</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>0.000514311119450328</v>
+        <v>-0.001606101733675702</v>
       </c>
       <c r="E22" s="40" t="n">
         <v>0.0005426623598601132</v>
@@ -1490,10 +1490,10 @@
         <v>0.0006017779632476739</v>
       </c>
       <c r="G22" s="41" t="n">
-        <v>0.9477552848568794</v>
+        <v>-2.959670418434256</v>
       </c>
       <c r="H22" s="41" t="n">
-        <v>0.8546526308053805</v>
+        <v>-2.668927464555026</v>
       </c>
       <c r="I22" s="3" t="n"/>
     </row>
@@ -1501,14 +1501,14 @@
       <c r="A23" s="3" t="n"/>
       <c r="B23" s="38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C23" s="39" t="n">
-        <v>3.55288838</v>
+        <v>3.56662961</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>0.0004456924249089944</v>
+        <v>0.001818977611183437</v>
       </c>
       <c r="E23" s="40" t="n">
         <v>0.0005426623598601132</v>
@@ -1517,10 +1517,10 @@
         <v>0.0006017779632476739</v>
       </c>
       <c r="G23" s="41" t="n">
-        <v>0.8213070555029547</v>
+        <v>3.351950947274711</v>
       </c>
       <c r="H23" s="41" t="n">
-        <v>0.7406260317404821</v>
+        <v>3.022672351388181</v>
       </c>
       <c r="I23" s="3" t="n"/>
     </row>
@@ -1574,24 +1574,24 @@
       <c r="A26" s="3" t="n"/>
       <c r="B26" s="32" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr"/>
       <c r="D26" s="12" t="n">
-        <v>0.005489881762714477</v>
+        <v>0.005889406026924782</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0.01161832663695161</v>
+        <v>0.004220058245789859</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.5236754106617179</v>
+        <v>1.547877786144507</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>0.472519144474225</v>
+        <v>1.395574583076038</v>
       </c>
       <c r="I26" s="14" t="n"/>
     </row>
@@ -1604,19 +1604,19 @@
       </c>
       <c r="C27" s="34" t="inlineStr"/>
       <c r="D27" s="35" t="n">
-        <v>0.008926158856966904</v>
+        <v>0.008963739035592111</v>
       </c>
       <c r="E27" s="35" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F27" s="35" t="n">
-        <v>0.01285374137368023</v>
+        <v>0.01276619859936212</v>
       </c>
       <c r="G27" s="36" t="n">
-        <v>0.7696387658547014</v>
+        <v>0.7787498965206278</v>
       </c>
       <c r="H27" s="36" t="n">
-        <v>0.6944405210489469</v>
+        <v>0.7021462940455896</v>
       </c>
       <c r="I27" s="37" t="n"/>
     </row>
@@ -1629,19 +1629,19 @@
       </c>
       <c r="C28" s="34" t="inlineStr"/>
       <c r="D28" s="35" t="n">
-        <v>0.02868524059719935</v>
+        <v>0.03154496241405869</v>
       </c>
       <c r="E28" s="35" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F28" s="35" t="n">
-        <v>0.03914881930625902</v>
+        <v>0.03905900380096416</v>
       </c>
       <c r="G28" s="36" t="n">
-        <v>0.8128862109145544</v>
+        <v>0.8961979248277638</v>
       </c>
       <c r="H28" s="36" t="n">
-        <v>0.7327230068625139</v>
+        <v>0.8076233222640462</v>
       </c>
       <c r="I28" s="37" t="n"/>
     </row>
@@ -1654,19 +1654,19 @@
       </c>
       <c r="C29" s="34" t="inlineStr"/>
       <c r="D29" s="35" t="n">
-        <v>0.06446235942377854</v>
+        <v>0.06600367613831026</v>
       </c>
       <c r="E29" s="35" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F29" s="35" t="n">
-        <v>0.07987693752901182</v>
+        <v>0.07978360181905497</v>
       </c>
       <c r="G29" s="36" t="n">
-        <v>0.8969568254626602</v>
+        <v>0.9195887894081914</v>
       </c>
       <c r="H29" s="36" t="n">
-        <v>0.8070209176505471</v>
+        <v>0.8272837354222631</v>
       </c>
       <c r="I29" s="37" t="n"/>
     </row>
@@ -1679,19 +1679,19 @@
       </c>
       <c r="C30" s="34" t="inlineStr"/>
       <c r="D30" s="35" t="n">
-        <v>0.1390821727814675</v>
+        <v>0.1397955677663845</v>
       </c>
       <c r="E30" s="35" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F30" s="35" t="n">
-        <v>0.1650341981406351</v>
+        <v>0.1652362768066389</v>
       </c>
       <c r="G30" s="36" t="n">
-        <v>0.9409081870845053</v>
+        <v>0.9444623116259351</v>
       </c>
       <c r="H30" s="36" t="n">
-        <v>0.8427475901870204</v>
+        <v>0.846034360420591</v>
       </c>
       <c r="I30" s="37" t="n"/>
     </row>
@@ -1699,24 +1699,24 @@
       <c r="A31" s="3" t="n"/>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr"/>
       <c r="D31" s="35" t="n">
-        <v>0.02629800073614752</v>
+        <v>0.2644074379091075</v>
       </c>
       <c r="E31" s="35" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F31" s="35" t="n">
-        <v>0.03598299795768156</v>
+        <v>0.3165559174053354</v>
       </c>
       <c r="G31" s="36" t="n">
-        <v>0.8106902355895298</v>
+        <v>0.9513438338699164</v>
       </c>
       <c r="H31" s="36" t="n">
-        <v>0.730845183246703</v>
+        <v>0.8352629768425583</v>
       </c>
       <c r="I31" s="37" t="n"/>
     </row>
@@ -1724,24 +1724,24 @@
       <c r="A32" s="3" t="n"/>
       <c r="B32" s="34" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C32" s="34" t="inlineStr"/>
       <c r="D32" s="35" t="n">
-        <v>0.1436344393419307</v>
+        <v>0.03320717708428877</v>
       </c>
       <c r="E32" s="35" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F32" s="35" t="n">
-        <v>0.1602797424224323</v>
+        <v>0.04223422499971918</v>
       </c>
       <c r="G32" s="36" t="n">
-        <v>1.003505055151759</v>
+        <v>0.8726012814833749</v>
       </c>
       <c r="H32" s="36" t="n">
-        <v>0.896148428809978</v>
+        <v>0.7862622573164199</v>
       </c>
       <c r="I32" s="37" t="n"/>
     </row>
@@ -1749,24 +1749,24 @@
       <c r="A33" s="3" t="n"/>
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C33" s="34" t="inlineStr"/>
       <c r="D33" s="35" t="n">
-        <v>0.1130111764854058</v>
+        <v>0.1436344393419307</v>
       </c>
       <c r="E33" s="35" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F33" s="35" t="n">
-        <v>0.1259760418445097</v>
+        <v>0.1602797424224323</v>
       </c>
       <c r="G33" s="36" t="n">
-        <v>1.034854197277371</v>
+        <v>1.003505055151759</v>
       </c>
       <c r="H33" s="36" t="n">
-        <v>0.8970846744406668</v>
+        <v>0.896148428809978</v>
       </c>
       <c r="I33" s="37" t="n"/>
     </row>
@@ -1774,130 +1774,144 @@
       <c r="A34" s="3" t="n"/>
       <c r="B34" s="34" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C34" s="34" t="inlineStr"/>
       <c r="D34" s="35" t="n">
-        <v>2.55189716</v>
+        <v>0.1130111764854058</v>
       </c>
       <c r="E34" s="35" t="n">
-        <v>2.170180757863388</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F34" s="35" t="n">
-        <v>2.802213103120176</v>
+        <v>0.1259760418445097</v>
       </c>
       <c r="G34" s="36" t="n">
-        <v>1.175891524590064</v>
+        <v>1.034854197277371</v>
       </c>
       <c r="H34" s="36" t="n">
-        <v>0.9106720531563223</v>
+        <v>0.8970846744406668</v>
       </c>
       <c r="I34" s="37" t="n"/>
     </row>
     <row r="35" ht="15.95" customHeight="1">
       <c r="A35" s="3" t="n"/>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="3" t="n"/>
-    </row>
-    <row r="36" ht="26.1" customHeight="1">
-      <c r="B36" s="31" t="inlineStr">
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="inlineStr"/>
+      <c r="D35" s="35" t="n">
+        <v>2.57580901</v>
+      </c>
+      <c r="E35" s="35" t="n">
+        <v>2.187426206741685</v>
+      </c>
+      <c r="F35" s="35" t="n">
+        <v>2.825156044671024</v>
+      </c>
+      <c r="G35" s="36" t="n">
+        <v>1.17755241391061</v>
+      </c>
+      <c r="H35" s="36" t="n">
+        <v>0.9117404381462905</v>
+      </c>
+      <c r="I35" s="37" t="n"/>
+    </row>
+    <row r="36" ht="15.95" customHeight="1">
+      <c r="A36" s="3" t="n"/>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="3" t="n"/>
+    </row>
+    <row r="37" ht="26.1" customHeight="1">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="3" t="n"/>
-    </row>
-    <row r="37" ht="15.95" customHeight="1">
-      <c r="B37" s="17" t="inlineStr">
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="31" t="n"/>
+      <c r="I37" s="3" t="n"/>
+    </row>
+    <row r="38" ht="15.95" customHeight="1">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="50" t="n">
-        <v>175606813.37</v>
-      </c>
-      <c r="I37" s="3" t="n"/>
-    </row>
-    <row r="38" ht="15.95" customHeight="1">
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
         </is>
       </c>
       <c r="C38" s="18" t="n"/>
       <c r="D38" s="12" t="n"/>
       <c r="E38" s="50" t="n">
-        <v>166268218.2321429</v>
+        <v>176789022.06</v>
       </c>
       <c r="I38" s="3" t="n"/>
     </row>
     <row r="39" ht="15.95" customHeight="1">
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="50" t="n">
+        <v>166526916.2584127</v>
+      </c>
       <c r="I39" s="3" t="n"/>
     </row>
     <row r="40" ht="15.95" customHeight="1">
-      <c r="A40" s="3" t="n"/>
-      <c r="B40" s="21" t="inlineStr">
-        <is>
-          <t>¹Data de Referência:</t>
-        </is>
-      </c>
-      <c r="C40" s="22" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="23" t="n"/>
-      <c r="H40" s="23" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
     </row>
     <row r="41" ht="15.95" customHeight="1">
       <c r="A41" s="3" t="n"/>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">²Cota Inicial em: </t>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>¹Data de Referência:</t>
         </is>
       </c>
       <c r="C41" s="22" t="inlineStr">
         <is>
-          <t>2013-12-23</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="n"/>
-      <c r="E41" s="25" t="n"/>
-      <c r="F41" s="25" t="n"/>
-      <c r="G41" s="25" t="n"/>
-      <c r="H41" s="25" t="n"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="23" t="n"/>
       <c r="I41" s="3" t="n"/>
     </row>
     <row r="42" ht="15.95" customHeight="1">
       <c r="A42" s="3" t="n"/>
-      <c r="B42" s="24" t="n"/>
-      <c r="C42" s="22" t="n"/>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">²Cota Inicial em: </t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>2013-12-23</t>
+        </is>
+      </c>
       <c r="D42" s="25" t="n"/>
       <c r="E42" s="25" t="n"/>
       <c r="F42" s="25" t="n"/>
@@ -1905,43 +1919,44 @@
       <c r="H42" s="25" t="n"/>
       <c r="I42" s="3" t="n"/>
     </row>
-    <row r="43" ht="43.5" customHeight="1">
+    <row r="43" ht="15.95" customHeight="1">
       <c r="A43" s="3" t="n"/>
-      <c r="B43" s="52" t="inlineStr">
+      <c r="B43" s="24" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="25" t="n"/>
+      <c r="E43" s="25" t="n"/>
+      <c r="F43" s="25" t="n"/>
+      <c r="G43" s="25" t="n"/>
+      <c r="H43" s="25" t="n"/>
+      <c r="I43" s="3" t="n"/>
+    </row>
+    <row r="44" ht="43.5" customHeight="1">
+      <c r="A44" s="3" t="n"/>
+      <c r="B44" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir. </t>
         </is>
       </c>
-      <c r="I43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="n"/>
-      <c r="B44" s="53" t="n"/>
       <c r="I44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
-      <c r="B45" s="26" t="n"/>
-      <c r="C45" s="26" t="n"/>
-      <c r="D45" s="26" t="n"/>
-      <c r="E45" s="26" t="n"/>
-      <c r="F45" s="26" t="n"/>
-      <c r="G45" s="26" t="n"/>
-      <c r="H45" s="26" t="n"/>
+      <c r="B45" s="52" t="n"/>
       <c r="I45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
-      <c r="B46" s="27" t="n"/>
-      <c r="C46" s="28" t="n"/>
-      <c r="D46" s="15" t="n"/>
-      <c r="E46" s="15" t="n"/>
-      <c r="F46" s="15" t="n"/>
-      <c r="G46" s="15" t="n"/>
-      <c r="H46" s="15" t="n"/>
+      <c r="B46" s="26" t="n"/>
+      <c r="C46" s="26" t="n"/>
+      <c r="D46" s="26" t="n"/>
+      <c r="E46" s="26" t="n"/>
+      <c r="F46" s="26" t="n"/>
+      <c r="G46" s="26" t="n"/>
+      <c r="H46" s="26" t="n"/>
       <c r="I46" s="3" t="n"/>
     </row>
     <row r="47">
+      <c r="A47" s="3" t="n"/>
       <c r="B47" s="27" t="n"/>
       <c r="C47" s="28" t="n"/>
       <c r="D47" s="15" t="n"/>
@@ -1949,16 +1964,26 @@
       <c r="F47" s="15" t="n"/>
       <c r="G47" s="15" t="n"/>
       <c r="H47" s="15" t="n"/>
+      <c r="I47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="27" t="n"/>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="15" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="15" t="n"/>
+      <c r="G48" s="15" t="n"/>
+      <c r="H48" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="E38:H38"/>
     <mergeCell ref="B44:H44"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="B45:H45"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="74" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="76"/>
 </worksheet>
 </file>